--- a/output/pdf_financials_xlsx/ELM.xlsx
+++ b/output/pdf_financials_xlsx/ELM.xlsx
@@ -1256,16 +1256,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.248285</v>
+        <v>-0.248285</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.322545</v>
+        <v>-0.322545</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.81086</v>
+        <v>-1.81086</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.192529</v>
+        <v>-0.192529</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-0.112617</v>
@@ -1325,7 +1325,7 @@
         <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.133739</v>
+        <v>0.09149500000000001</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0.13185</v>
@@ -1544,19 +1544,19 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.248285</v>
+        <v>-0.248285</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.322545</v>
+        <v>-0.322545</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.81086</v>
+        <v>-1.81086</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.192529</v>
+        <v>-0.192529</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.021122</v>
+        <v>-0.021122</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-2.270513</v>
@@ -1715,19 +1715,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.248285</v>
+        <v>-0.248285</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.322545</v>
+        <v>-0.322545</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.81086</v>
+        <v>-1.81086</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.192529</v>
+        <v>-0.192529</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.021122</v>
+        <v>-0.021122</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-2.270513</v>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-0.017172</v>
+        <v>0.017172</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>37.841883</v>
@@ -1977,16 +1977,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.248285</v>
+        <v>-0.248285</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.322545</v>
+        <v>-0.322545</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.81086</v>
+        <v>-1.81086</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.192529</v>
+        <v>-0.192529</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.112617</v>
@@ -2091,16 +2091,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.248285</v>
+        <v>-0.248285</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.322545</v>
+        <v>-0.322545</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.81086</v>
+        <v>-1.81086</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.192529</v>
+        <v>-0.192529</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.112617</v>
@@ -2223,19 +2223,19 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-118.7556052816182</v>
+        <v>-81.24439471838177</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-6.165066679509581</v>
@@ -5679,16 +5679,16 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.44745</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.574555</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.574555</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.574555</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0</v>
@@ -6041,13 +6041,13 @@
         </is>
       </c>
       <c r="C99" s="3" t="n">
-        <v>0.248285</v>
+        <v>-0.248285</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.322545</v>
+        <v>-0.322545</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>1.81086</v>
+        <v>-1.81086</v>
       </c>
       <c r="F99" s="3" t="n">
         <v>-0.192529</v>
@@ -21068,7 +21068,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -21928,7 +21932,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -49620,10 +49628,10 @@
         </is>
       </c>
       <c r="I437" s="5" t="n">
-        <v>0.192529</v>
+        <v>-0.192529</v>
       </c>
       <c r="J437" s="5" t="n">
-        <v>0.021122</v>
+        <v>-0.021122</v>
       </c>
       <c r="K437" t="inlineStr">
         <is>
@@ -50470,10 +50478,10 @@
         </is>
       </c>
       <c r="G446" s="5" t="n">
-        <v>0.322545</v>
+        <v>-0.322545</v>
       </c>
       <c r="H446" s="5" t="n">
-        <v>1.81086</v>
+        <v>-1.81086</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
@@ -52859,10 +52867,10 @@
         </is>
       </c>
       <c r="F471" s="5" t="n">
-        <v>0.248285</v>
+        <v>-0.248285</v>
       </c>
       <c r="G471" s="5" t="n">
-        <v>0.322545</v>
+        <v>-0.322545</v>
       </c>
       <c r="H471" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ELM.xlsx
+++ b/output/pdf_financials_xlsx/ELM.xlsx
@@ -1043,7 +1043,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002617</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1064,13 +1064,13 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.06963999999999999</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.080668</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.072033</v>
       </c>
     </row>
     <row r="13">
@@ -1992,7 +1992,7 @@
         <v>-0.112617</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.138663</v>
+        <v>-2.14128</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-1.751832</v>
@@ -2013,13 +2013,13 @@
         <v>-0.021912</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.7711519999999999</v>
+        <v>-0.840792</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.478365</v>
+        <v>-0.559033</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.210706</v>
+        <v>-0.282739</v>
       </c>
     </row>
     <row r="28">
@@ -2106,7 +2106,7 @@
         <v>-0.112617</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.138663</v>
+        <v>-2.14128</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-1.751832</v>
@@ -2127,13 +2127,13 @@
         <v>-0.021912</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.761379</v>
+        <v>-0.831019</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.467458</v>
+        <v>-0.548126</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.200071</v>
+        <v>-0.272104</v>
       </c>
     </row>
     <row r="30">
@@ -2202,13 +2202,13 @@
         <v>-1.047074384714778</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-71.68929263483777</v>
+        <v>-78.24639801742661</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-44.85915837617328</v>
+        <v>-52.60038558351414</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-18.70436002838314</v>
+        <v>-25.43862519387201</v>
       </c>
     </row>
     <row r="31">
@@ -2372,37 +2372,37 @@
         <v>0.000402</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.751165</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>3.737092</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>4.244764</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.4393</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.47444</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.335908</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.10205</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.232427</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.189298</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.038704</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.042928</v>
       </c>
     </row>
     <row r="35">
@@ -2482,37 +2482,37 @@
         <v>0.000402</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.751165</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>3.737092</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>4.244764</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.4393</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2.47444</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.335908</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.10205</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.232427</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.189298</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.038704</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.042928</v>
       </c>
     </row>
     <row r="37">
@@ -3142,31 +3142,31 @@
         <v>0.01883</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.752035</v>
+        <v>0.00087</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>3.737962</v>
+        <v>0.00087</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>4.250669</v>
+        <v>0.005905</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.469514</v>
+        <v>0.030214</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.25738</v>
+        <v>1.78294</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.242435</v>
+        <v>1.906527</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.520603</v>
+        <v>1.418553</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.297018</v>
+        <v>0.064591</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.321506</v>
+        <v>0.132208</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -38836,7 +38836,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -40030,7 +40030,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -40206,7 +40206,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -41886,7 +41886,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -47896,7 +47896,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">

--- a/output/pdf_financials_xlsx/ELM.xlsx
+++ b/output/pdf_financials_xlsx/ELM.xlsx
@@ -1349,7 +1349,7 @@
         <v>-0</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>0.177528</v>
+        <v>-0.177528</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>-0</v>
@@ -6164,13 +6164,13 @@
         <v>0</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.077921</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>-0.04375</v>
+        <v>0.017527</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0.04375</v>
+        <v>-0.021721</v>
       </c>
       <c r="I101" s="3" t="n">
         <v>0.013627</v>
@@ -6449,7 +6449,7 @@
         <v>0.004227</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.031399</v>
+        <v>0.10932</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>0.090325</v>
@@ -6692,25 +6692,25 @@
         <v>0</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.121639</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.19943</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.221822</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.485475</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.269996</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.280562</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.14496</v>
       </c>
     </row>
     <row r="111">
@@ -6737,10 +6737,10 @@
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.117995</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.02271</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>-0.41056</v>
@@ -8094,10 +8094,10 @@
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.117995</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.02271</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>-0.41056</v>
@@ -8159,10 +8159,10 @@
         </is>
       </c>
       <c r="G135" s="3" t="n">
-        <v>0.090325</v>
+        <v>-0.02767</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.945537</v>
+        <v>-0.968247</v>
       </c>
       <c r="I135" s="1" t="inlineStr">
         <is>
@@ -22688,7 +22688,11 @@
           <t>Accretion expense (Note 5, 6 and 11 )</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -24176,7 +24180,11 @@
           <t>Accretion expense (Note 5, 6 and11)</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -25510,7 +25518,11 @@
           <t>Accretion expense (Note 5&amp;6&amp;11 )</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -26762,7 +26774,11 @@
           <t>Accretion expense (Note 11 )</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -28076,7 +28092,11 @@
           <t>Accretion expense (Note 15)</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -29710,7 +29730,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -32308,7 +32332,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -32694,7 +32722,11 @@
           <t>GST receivables</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -33084,7 +33116,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -34442,7 +34478,11 @@
           <t>(Increase)/ Decrease in GST Receivable</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -34912,7 +34952,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -40386,7 +40430,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -41220,7 +41268,11 @@
           <t>Income tax recovery (Note 14)</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
